--- a/education_forms/040_high_school_senior_survey--education_forms.xlsx
+++ b/education_forms/040_high_school_senior_survey--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -757,8 +757,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -786,12 +786,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'college'}</t>
+          <t>college</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'College'}</t>
+          <t>College</t>
         </is>
       </c>
     </row>
@@ -803,12 +803,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'university'}</t>
+          <t>university</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'University'}</t>
+          <t>University</t>
         </is>
       </c>
     </row>
@@ -820,12 +820,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'community_college'}</t>
+          <t>community_college</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Community College'}</t>
+          <t>Community College</t>
         </is>
       </c>
     </row>
@@ -837,12 +837,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'math'}</t>
+          <t>math</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Math'}</t>
+          <t>Math</t>
         </is>
       </c>
     </row>
@@ -871,12 +871,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'science'}</t>
+          <t>science</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Science'}</t>
+          <t>Science</t>
         </is>
       </c>
     </row>
@@ -888,12 +888,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'English'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -905,12 +905,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'history'}</t>
+          <t>history</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'History'}</t>
+          <t>History</t>
         </is>
       </c>
     </row>
@@ -922,12 +922,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -939,12 +939,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'positive'}</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Positive'}</t>
+          <t>Positive</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'negative'}</t>
+          <t>negative</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Negative'}</t>
+          <t>Negative</t>
         </is>
       </c>
     </row>
@@ -973,12 +973,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -990,12 +990,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'strong_commitment'}</t>
+          <t>strong_commitment</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Strong Commitment'}</t>
+          <t>Strong Commitment</t>
         </is>
       </c>
     </row>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'somewhat_commitment'}</t>
+          <t>somewhat_commitment</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Somewhat Commitment'}</t>
+          <t>Somewhat Commitment</t>
         </is>
       </c>
     </row>
@@ -1024,12 +1024,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'no_commitment'}</t>
+          <t>no_commitment</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'No Commitment'}</t>
+          <t>No Commitment</t>
         </is>
       </c>
     </row>
@@ -1041,12 +1041,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'class_officer'}</t>
+          <t>class_officer</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Class Officer'}</t>
+          <t>Class Officer</t>
         </is>
       </c>
     </row>
@@ -1058,12 +1058,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'school_organization'}</t>
+          <t>school_organization</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'School Organization'}</t>
+          <t>School Organization</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'student_club'}</t>
+          <t>student_club</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'Student Club'}</t>
+          <t>Student Club</t>
         </is>
       </c>
     </row>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'sports'}</t>
+          <t>sports</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'Sports'}</t>
+          <t>Sports</t>
         </is>
       </c>
     </row>
@@ -1126,12 +1126,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'clubs'}</t>
+          <t>clubs</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'Clubs'}</t>
+          <t>Clubs</t>
         </is>
       </c>
     </row>
@@ -1143,12 +1143,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'organizations'}</t>
+          <t>organizations</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 'Organizations'}</t>
+          <t>Organizations</t>
         </is>
       </c>
     </row>
@@ -1160,12 +1160,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1177,12 +1177,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 'Very Satisfied'}</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
@@ -1194,12 +1194,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': 'Somewhat Satisfied'}</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
@@ -1211,12 +1211,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'value':_'not_satisfied'}</t>
+          <t>not_satisfied</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'value': 'Not Satisfied'}</t>
+          <t>Not Satisfied</t>
         </is>
       </c>
     </row>
